--- a/archivo_con_ganancia.xlsx
+++ b/archivo_con_ganancia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M301"/>
+  <dimension ref="A1:P301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Volumen Huevos</t>
+          <t>Volumen Huevos (u)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -492,6 +492,21 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Ganancia ($)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ingreso Total ($)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ganancia Harina ($)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ganancia Huevos ($)</t>
         </is>
       </c>
     </row>
@@ -529,7 +544,7 @@
         <v>21000</v>
       </c>
       <c r="I2" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J2" t="n">
         <v>18500</v>
@@ -543,7 +558,16 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N2" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="3">
@@ -580,7 +604,7 @@
         <v>84000</v>
       </c>
       <c r="I3" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J3" t="n">
         <v>18500</v>
@@ -594,7 +618,16 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N3" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O3" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P3" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="4">
@@ -647,6 +680,15 @@
       <c r="M4" t="n">
         <v>65500</v>
       </c>
+      <c r="N4" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -682,7 +724,7 @@
         <v>84000</v>
       </c>
       <c r="I5" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J5" t="n">
         <v>18500</v>
@@ -696,7 +738,16 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>208380</v>
+        <v>217740</v>
+      </c>
+      <c r="N5" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O5" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P5" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="6">
@@ -749,6 +800,15 @@
       <c r="M6" t="n">
         <v>44500</v>
       </c>
+      <c r="N6" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -784,7 +844,7 @@
         <v>42000</v>
       </c>
       <c r="I7" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J7" t="n">
         <v>18500</v>
@@ -798,7 +858,16 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>163500</v>
+        <v>175740</v>
+      </c>
+      <c r="N7" t="n">
+        <v>234240</v>
+      </c>
+      <c r="O7" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P7" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="8">
@@ -851,6 +920,15 @@
       <c r="M8" t="n">
         <v>23500</v>
       </c>
+      <c r="N8" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -886,7 +964,7 @@
         <v>42000</v>
       </c>
       <c r="I9" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J9" t="n">
         <v>18500</v>
@@ -900,7 +978,16 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>73500</v>
+        <v>79620</v>
+      </c>
+      <c r="N9" t="n">
+        <v>138120</v>
+      </c>
+      <c r="O9" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P9" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="10">
@@ -937,7 +1024,7 @@
         <v>21000</v>
       </c>
       <c r="I10" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J10" t="n">
         <v>18500</v>
@@ -951,7 +1038,16 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N10" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="11">
@@ -1004,6 +1100,15 @@
       <c r="M11" t="n">
         <v>86500</v>
       </c>
+      <c r="N11" t="n">
+        <v>105000</v>
+      </c>
+      <c r="O11" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1055,6 +1160,15 @@
       <c r="M12" t="n">
         <v>65500</v>
       </c>
+      <c r="N12" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O12" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1090,7 +1204,7 @@
         <v>21000</v>
       </c>
       <c r="I13" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J13" t="n">
         <v>18500</v>
@@ -1104,7 +1218,16 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N13" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P13" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="14">
@@ -1141,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1155,7 +1278,16 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N14" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="15">
@@ -1192,7 +1324,7 @@
         <v>42000</v>
       </c>
       <c r="I15" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J15" t="n">
         <v>18500</v>
@@ -1206,7 +1338,16 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N15" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P15" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="16">
@@ -1243,7 +1384,7 @@
         <v>84000</v>
       </c>
       <c r="I16" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J16" t="n">
         <v>18500</v>
@@ -1257,7 +1398,16 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N16" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O16" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P16" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="17">
@@ -1294,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1308,7 +1458,16 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N17" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="18">
@@ -1345,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1359,7 +1518,16 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N18" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="19">
@@ -1396,7 +1564,7 @@
         <v>21000</v>
       </c>
       <c r="I19" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J19" t="n">
         <v>18500</v>
@@ -1410,7 +1578,16 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N19" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1624,7 @@
         <v>21000</v>
       </c>
       <c r="I20" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J20" t="n">
         <v>18500</v>
@@ -1461,7 +1638,16 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N20" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P20" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="21">
@@ -1498,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1512,7 +1698,16 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N21" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="22">
@@ -1549,7 +1744,7 @@
         <v>21000</v>
       </c>
       <c r="I22" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J22" t="n">
         <v>18500</v>
@@ -1563,7 +1758,16 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N22" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P22" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="23">
@@ -1600,7 +1804,7 @@
         <v>63000</v>
       </c>
       <c r="I23" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J23" t="n">
         <v>18500</v>
@@ -1614,7 +1818,16 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>94500</v>
+        <v>100620</v>
+      </c>
+      <c r="N23" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O23" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P23" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="24">
@@ -1651,7 +1864,7 @@
         <v>21000</v>
       </c>
       <c r="I24" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J24" t="n">
         <v>18500</v>
@@ -1665,7 +1878,16 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N24" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P24" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="25">
@@ -1702,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1716,7 +1938,16 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N25" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="26">
@@ -1753,7 +1984,7 @@
         <v>42000</v>
       </c>
       <c r="I26" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J26" t="n">
         <v>18500</v>
@@ -1767,7 +1998,16 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>28500</v>
+        <v>31560</v>
+      </c>
+      <c r="N26" t="n">
+        <v>90060</v>
+      </c>
+      <c r="O26" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P26" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="27">
@@ -1804,7 +2044,7 @@
         <v>21000</v>
       </c>
       <c r="I27" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J27" t="n">
         <v>18500</v>
@@ -1818,7 +2058,16 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N27" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P27" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="28">
@@ -1855,7 +2104,7 @@
         <v>21000</v>
       </c>
       <c r="I28" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J28" t="n">
         <v>18500</v>
@@ -1869,7 +2118,16 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N28" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P28" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="29">
@@ -1906,7 +2164,7 @@
         <v>21000</v>
       </c>
       <c r="I29" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J29" t="n">
         <v>18500</v>
@@ -1920,7 +2178,16 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N29" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P29" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="30">
@@ -1957,7 +2224,7 @@
         <v>21000</v>
       </c>
       <c r="I30" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J30" t="n">
         <v>18500</v>
@@ -1971,7 +2238,16 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N30" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P30" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="31">
@@ -2008,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>40000</v>
+        <v>48060</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2022,7 +2298,16 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>8060</v>
+      </c>
+      <c r="N31" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="32">
@@ -2075,6 +2360,15 @@
       <c r="M32" t="n">
         <v>86500</v>
       </c>
+      <c r="N32" t="n">
+        <v>105000</v>
+      </c>
+      <c r="O32" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2110,7 +2404,7 @@
         <v>42000</v>
       </c>
       <c r="I33" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J33" t="n">
         <v>18500</v>
@@ -2124,7 +2418,16 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>163500</v>
+        <v>175740</v>
+      </c>
+      <c r="N33" t="n">
+        <v>234240</v>
+      </c>
+      <c r="O33" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P33" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="34">
@@ -2177,6 +2480,15 @@
       <c r="M34" t="n">
         <v>23500</v>
       </c>
+      <c r="N34" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2212,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2226,7 +2538,16 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N35" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="36">
@@ -2263,7 +2584,7 @@
         <v>63000</v>
       </c>
       <c r="I36" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J36" t="n">
         <v>18500</v>
@@ -2277,7 +2598,16 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N36" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O36" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P36" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="37">
@@ -2314,7 +2644,7 @@
         <v>21000</v>
       </c>
       <c r="I37" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J37" t="n">
         <v>18500</v>
@@ -2328,7 +2658,16 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N37" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P37" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="38">
@@ -2365,7 +2704,7 @@
         <v>42000</v>
       </c>
       <c r="I38" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J38" t="n">
         <v>18500</v>
@@ -2379,7 +2718,16 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>28500</v>
+        <v>31560</v>
+      </c>
+      <c r="N38" t="n">
+        <v>90060</v>
+      </c>
+      <c r="O38" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P38" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="39">
@@ -2416,7 +2764,7 @@
         <v>21000</v>
       </c>
       <c r="I39" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J39" t="n">
         <v>18500</v>
@@ -2430,7 +2778,16 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N39" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P39" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="40">
@@ -2467,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2481,7 +2838,16 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N40" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="41">
@@ -2534,6 +2900,15 @@
       <c r="M41" t="n">
         <v>23500</v>
       </c>
+      <c r="N41" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2585,6 +2960,15 @@
       <c r="M42" t="n">
         <v>2500</v>
       </c>
+      <c r="N42" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2620,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2634,7 +3018,16 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N43" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="44">
@@ -2671,7 +3064,7 @@
         <v>21000</v>
       </c>
       <c r="I44" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J44" t="n">
         <v>18500</v>
@@ -2685,7 +3078,16 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N44" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P44" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="45">
@@ -2722,7 +3124,7 @@
         <v>42000</v>
       </c>
       <c r="I45" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J45" t="n">
         <v>18500</v>
@@ -2736,7 +3138,16 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>28500</v>
+        <v>31560</v>
+      </c>
+      <c r="N45" t="n">
+        <v>90060</v>
+      </c>
+      <c r="O45" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P45" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="46">
@@ -2789,6 +3200,15 @@
       <c r="M46" t="n">
         <v>65500</v>
       </c>
+      <c r="N46" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O46" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2824,7 +3244,7 @@
         <v>21000</v>
       </c>
       <c r="I47" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J47" t="n">
         <v>18500</v>
@@ -2838,7 +3258,16 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>142500</v>
+        <v>154740</v>
+      </c>
+      <c r="N47" t="n">
+        <v>213240</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P47" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="48">
@@ -2875,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2889,7 +3318,16 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N48" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="49">
@@ -2942,6 +3380,15 @@
       <c r="M49" t="n">
         <v>65500</v>
       </c>
+      <c r="N49" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O49" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2977,7 +3424,7 @@
         <v>84000</v>
       </c>
       <c r="I50" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J50" t="n">
         <v>18500</v>
@@ -2991,7 +3438,16 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N50" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O50" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P50" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="51">
@@ -3028,7 +3484,7 @@
         <v>63000</v>
       </c>
       <c r="I51" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J51" t="n">
         <v>18500</v>
@@ -3042,7 +3498,16 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N51" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O51" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P51" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="52">
@@ -3076,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>840000</v>
+        <v>84000</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3093,7 +3558,16 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>821500</v>
+        <v>65500</v>
+      </c>
+      <c r="N52" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O52" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3130,7 +3604,7 @@
         <v>63000</v>
       </c>
       <c r="I53" t="n">
-        <v>135000</v>
+        <v>96120</v>
       </c>
       <c r="J53" t="n">
         <v>18500</v>
@@ -3144,7 +3618,16 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>139500</v>
+        <v>100620</v>
+      </c>
+      <c r="N53" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O53" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P53" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="54">
@@ -3181,7 +3664,7 @@
         <v>63000</v>
       </c>
       <c r="I54" t="n">
-        <v>135000</v>
+        <v>96120</v>
       </c>
       <c r="J54" t="n">
         <v>18500</v>
@@ -3195,7 +3678,16 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>139500</v>
+        <v>100620</v>
+      </c>
+      <c r="N54" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O54" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P54" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="55">
@@ -3232,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3246,7 +3738,16 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N55" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="56">
@@ -3283,7 +3784,7 @@
         <v>42000</v>
       </c>
       <c r="I56" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J56" t="n">
         <v>18500</v>
@@ -3297,7 +3798,16 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>28500</v>
+        <v>31560</v>
+      </c>
+      <c r="N56" t="n">
+        <v>90060</v>
+      </c>
+      <c r="O56" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P56" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="57">
@@ -3334,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3348,7 +3858,16 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N57" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="58">
@@ -3385,7 +3904,7 @@
         <v>21000</v>
       </c>
       <c r="I58" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J58" t="n">
         <v>18500</v>
@@ -3399,7 +3918,16 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N58" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P58" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="59">
@@ -3452,6 +3980,15 @@
       <c r="M59" t="n">
         <v>65500</v>
       </c>
+      <c r="N59" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O59" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3487,7 +4024,7 @@
         <v>21000</v>
       </c>
       <c r="I60" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J60" t="n">
         <v>18500</v>
@@ -3501,7 +4038,16 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N60" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P60" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="61">
@@ -3538,7 +4084,7 @@
         <v>105000</v>
       </c>
       <c r="I61" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J61" t="n">
         <v>18500</v>
@@ -3552,7 +4098,16 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>226500</v>
+        <v>238740</v>
+      </c>
+      <c r="N61" t="n">
+        <v>297240</v>
+      </c>
+      <c r="O61" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P61" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="62">
@@ -3589,7 +4144,7 @@
         <v>84000</v>
       </c>
       <c r="I62" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J62" t="n">
         <v>18500</v>
@@ -3603,7 +4158,16 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N62" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O62" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P62" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="63">
@@ -3640,7 +4204,7 @@
         <v>21000</v>
       </c>
       <c r="I63" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J63" t="n">
         <v>18500</v>
@@ -3654,7 +4218,16 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N63" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P63" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="64">
@@ -3691,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3705,7 +4278,16 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N64" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="65">
@@ -3742,7 +4324,7 @@
         <v>42000</v>
       </c>
       <c r="I65" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J65" t="n">
         <v>18500</v>
@@ -3756,7 +4338,16 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>166380</v>
+        <v>175740</v>
+      </c>
+      <c r="N65" t="n">
+        <v>234240</v>
+      </c>
+      <c r="O65" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P65" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="66">
@@ -3793,7 +4384,7 @@
         <v>21000</v>
       </c>
       <c r="I66" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J66" t="n">
         <v>18500</v>
@@ -3807,7 +4398,16 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N66" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P66" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="67">
@@ -3844,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J67" t="n">
         <v>10500</v>
@@ -3858,7 +4458,16 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-5500</v>
+        <v>-2440</v>
+      </c>
+      <c r="N67" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-10500</v>
+      </c>
+      <c r="P67" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="68">
@@ -3895,7 +4504,7 @@
         <v>21000</v>
       </c>
       <c r="I68" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J68" t="n">
         <v>18500</v>
@@ -3909,7 +4518,16 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N68" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P68" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="69">
@@ -3946,7 +4564,7 @@
         <v>84000</v>
       </c>
       <c r="I69" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J69" t="n">
         <v>18500</v>
@@ -3960,7 +4578,16 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>208380</v>
+        <v>217740</v>
+      </c>
+      <c r="N69" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O69" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P69" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="70">
@@ -4013,6 +4640,15 @@
       <c r="M70" t="n">
         <v>65500</v>
       </c>
+      <c r="N70" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O70" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4048,7 +4684,7 @@
         <v>21000</v>
       </c>
       <c r="I71" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J71" t="n">
         <v>18500</v>
@@ -4062,7 +4698,16 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N71" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O71" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P71" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="72">
@@ -4099,7 +4744,7 @@
         <v>21000</v>
       </c>
       <c r="I72" t="n">
-        <v>8000</v>
+        <v>8010</v>
       </c>
       <c r="J72" t="n">
         <v>18500</v>
@@ -4113,7 +4758,16 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>10500</v>
+        <v>10510</v>
+      </c>
+      <c r="N72" t="n">
+        <v>29010</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P72" t="n">
+        <v>8010</v>
       </c>
     </row>
     <row r="73">
@@ -4150,7 +4804,7 @@
         <v>21000</v>
       </c>
       <c r="I73" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J73" t="n">
         <v>18500</v>
@@ -4164,7 +4818,16 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N73" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P73" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="74">
@@ -4201,7 +4864,7 @@
         <v>21000</v>
       </c>
       <c r="I74" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4215,7 +4878,16 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>71000</v>
+        <v>77120</v>
+      </c>
+      <c r="N74" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O74" t="n">
+        <v>21000</v>
+      </c>
+      <c r="P74" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="75">
@@ -4252,7 +4924,7 @@
         <v>21000</v>
       </c>
       <c r="I75" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J75" t="n">
         <v>18500</v>
@@ -4266,7 +4938,16 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>137500</v>
+        <v>146680</v>
+      </c>
+      <c r="N75" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O75" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P75" t="n">
+        <v>144180</v>
       </c>
     </row>
     <row r="76">
@@ -4303,7 +4984,7 @@
         <v>84000</v>
       </c>
       <c r="I76" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J76" t="n">
         <v>18500</v>
@@ -4317,7 +4998,16 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N76" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O76" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P76" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="77">
@@ -4354,7 +5044,7 @@
         <v>21000</v>
       </c>
       <c r="I77" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J77" t="n">
         <v>18500</v>
@@ -4368,7 +5058,16 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N77" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O77" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P77" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="78">
@@ -4421,6 +5120,15 @@
       <c r="M78" t="n">
         <v>23500</v>
       </c>
+      <c r="N78" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O78" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4456,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4470,7 +5178,16 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N79" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="80">
@@ -4507,7 +5224,7 @@
         <v>21000</v>
       </c>
       <c r="I80" t="n">
-        <v>8000</v>
+        <v>8010</v>
       </c>
       <c r="J80" t="n">
         <v>18500</v>
@@ -4521,7 +5238,16 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>10500</v>
+        <v>10510</v>
+      </c>
+      <c r="N80" t="n">
+        <v>29010</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P80" t="n">
+        <v>8010</v>
       </c>
     </row>
     <row r="81">
@@ -4558,7 +5284,7 @@
         <v>21000</v>
       </c>
       <c r="I81" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J81" t="n">
         <v>18500</v>
@@ -4572,7 +5298,16 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N81" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O81" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P81" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="82">
@@ -4609,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4623,7 +5358,16 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N82" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="83">
@@ -4660,7 +5404,7 @@
         <v>21000</v>
       </c>
       <c r="I83" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J83" t="n">
         <v>18500</v>
@@ -4674,7 +5418,16 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N83" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P83" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="84">
@@ -4711,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -4725,7 +5478,16 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N84" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="85">
@@ -4762,7 +5524,7 @@
         <v>21000</v>
       </c>
       <c r="I85" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J85" t="n">
         <v>18500</v>
@@ -4776,7 +5538,16 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N85" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P85" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="86">
@@ -4813,7 +5584,7 @@
         <v>105000</v>
       </c>
       <c r="I86" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J86" t="n">
         <v>18500</v>
@@ -4827,7 +5598,16 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>181500</v>
+        <v>190680</v>
+      </c>
+      <c r="N86" t="n">
+        <v>249180</v>
+      </c>
+      <c r="O86" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P86" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="87">
@@ -4864,7 +5644,7 @@
         <v>63000</v>
       </c>
       <c r="I87" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J87" t="n">
         <v>18500</v>
@@ -4878,7 +5658,16 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>94500</v>
+        <v>100620</v>
+      </c>
+      <c r="N87" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O87" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P87" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="88">
@@ -4915,7 +5704,7 @@
         <v>21000</v>
       </c>
       <c r="I88" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J88" t="n">
         <v>18500</v>
@@ -4929,7 +5718,16 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N88" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O88" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P88" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="89">
@@ -4982,6 +5780,15 @@
       <c r="M89" t="n">
         <v>2500</v>
       </c>
+      <c r="N89" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5017,7 +5824,7 @@
         <v>21000</v>
       </c>
       <c r="I90" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J90" t="n">
         <v>10500</v>
@@ -5031,7 +5838,16 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>15500</v>
+        <v>18560</v>
+      </c>
+      <c r="N90" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O90" t="n">
+        <v>10500</v>
+      </c>
+      <c r="P90" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="91">
@@ -5068,7 +5884,7 @@
         <v>63000</v>
       </c>
       <c r="I91" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J91" t="n">
         <v>18500</v>
@@ -5082,7 +5898,16 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>184500</v>
+        <v>196740</v>
+      </c>
+      <c r="N91" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O91" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P91" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="92">
@@ -5119,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5133,7 +5958,16 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N92" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="93">
@@ -5170,7 +6004,7 @@
         <v>42000</v>
       </c>
       <c r="I93" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J93" t="n">
         <v>18500</v>
@@ -5184,7 +6018,16 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>73500</v>
+        <v>79620</v>
+      </c>
+      <c r="N93" t="n">
+        <v>138120</v>
+      </c>
+      <c r="O93" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P93" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="94">
@@ -5221,7 +6064,7 @@
         <v>21000</v>
       </c>
       <c r="I94" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J94" t="n">
         <v>18500</v>
@@ -5235,7 +6078,16 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>92500</v>
+        <v>98620</v>
+      </c>
+      <c r="N94" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O94" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P94" t="n">
+        <v>96120</v>
       </c>
     </row>
     <row r="95">
@@ -5272,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5286,7 +6138,16 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N95" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="96">
@@ -5323,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -5337,7 +6198,16 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N96" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="97">
@@ -5374,7 +6244,7 @@
         <v>21000</v>
       </c>
       <c r="I97" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J97" t="n">
         <v>18500</v>
@@ -5388,7 +6258,16 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N97" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P97" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="98">
@@ -5425,7 +6304,7 @@
         <v>21000</v>
       </c>
       <c r="I98" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J98" t="n">
         <v>18500</v>
@@ -5439,7 +6318,16 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N98" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O98" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P98" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="99">
@@ -5476,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -5490,7 +6378,16 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>142880</v>
+        <v>152240</v>
+      </c>
+      <c r="N99" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="100">
@@ -5527,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5541,7 +6438,16 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N100" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="101">
@@ -5594,6 +6500,15 @@
       <c r="M101" t="n">
         <v>2500</v>
       </c>
+      <c r="N101" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O101" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5629,7 +6544,7 @@
         <v>21000</v>
       </c>
       <c r="I102" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J102" t="n">
         <v>18500</v>
@@ -5643,7 +6558,16 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N102" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O102" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P102" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="103">
@@ -5680,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -5694,7 +6618,16 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N103" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="104">
@@ -5747,6 +6680,15 @@
       <c r="M104" t="n">
         <v>44500</v>
       </c>
+      <c r="N104" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O104" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5782,7 +6724,7 @@
         <v>21000</v>
       </c>
       <c r="I105" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J105" t="n">
         <v>18500</v>
@@ -5796,7 +6738,16 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N105" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O105" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P105" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="106">
@@ -5833,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5847,7 +6798,16 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N106" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="107">
@@ -5884,7 +6844,7 @@
         <v>21000</v>
       </c>
       <c r="I107" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J107" t="n">
         <v>18500</v>
@@ -5898,7 +6858,16 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N107" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O107" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P107" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="108">
@@ -5935,7 +6904,7 @@
         <v>21000</v>
       </c>
       <c r="I108" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J108" t="n">
         <v>18500</v>
@@ -5949,7 +6918,16 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N108" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O108" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P108" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="109">
@@ -5986,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -6000,7 +6978,16 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N109" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="110">
@@ -6037,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -6051,7 +7038,16 @@
         </is>
       </c>
       <c r="M110" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N110" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="111">
@@ -6088,7 +7084,7 @@
         <v>105000</v>
       </c>
       <c r="I111" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J111" t="n">
         <v>18500</v>
@@ -6102,7 +7098,16 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>226500</v>
+        <v>238740</v>
+      </c>
+      <c r="N111" t="n">
+        <v>297240</v>
+      </c>
+      <c r="O111" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P111" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="112">
@@ -6155,6 +7160,15 @@
       <c r="M112" t="n">
         <v>65500</v>
       </c>
+      <c r="N112" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O112" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6190,7 +7204,7 @@
         <v>21000</v>
       </c>
       <c r="I113" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J113" t="n">
         <v>18500</v>
@@ -6204,7 +7218,16 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N113" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O113" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P113" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="114">
@@ -6241,7 +7264,7 @@
         <v>63000</v>
       </c>
       <c r="I114" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J114" t="n">
         <v>18500</v>
@@ -6255,7 +7278,16 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N114" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O114" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P114" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="115">
@@ -6292,7 +7324,7 @@
         <v>21000</v>
       </c>
       <c r="I115" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J115" t="n">
         <v>18500</v>
@@ -6306,7 +7338,16 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N115" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O115" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P115" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="116">
@@ -6343,7 +7384,7 @@
         <v>21000</v>
       </c>
       <c r="I116" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J116" t="n">
         <v>18500</v>
@@ -6357,7 +7398,16 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N116" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O116" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P116" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="117">
@@ -6410,6 +7460,15 @@
       <c r="M117" t="n">
         <v>2500</v>
       </c>
+      <c r="N117" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O117" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6445,7 +7504,7 @@
         <v>21000</v>
       </c>
       <c r="I118" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J118" t="n">
         <v>18500</v>
@@ -6459,7 +7518,16 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N118" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O118" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P118" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="119">
@@ -6496,7 +7564,7 @@
         <v>84000</v>
       </c>
       <c r="I119" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J119" t="n">
         <v>18500</v>
@@ -6510,7 +7578,16 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N119" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O119" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P119" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="120">
@@ -6547,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -6561,7 +7638,16 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N120" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="121">
@@ -6598,7 +7684,7 @@
         <v>21000</v>
       </c>
       <c r="I121" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J121" t="n">
         <v>18500</v>
@@ -6612,7 +7698,16 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N121" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O121" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P121" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="122">
@@ -6649,7 +7744,7 @@
         <v>84000</v>
       </c>
       <c r="I122" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J122" t="n">
         <v>18500</v>
@@ -6663,7 +7758,16 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N122" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O122" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P122" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="123">
@@ -6700,7 +7804,7 @@
         <v>84000</v>
       </c>
       <c r="I123" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J123" t="n">
         <v>18500</v>
@@ -6714,7 +7818,16 @@
         </is>
       </c>
       <c r="M123" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N123" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O123" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P123" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="124">
@@ -6751,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -6765,7 +7878,16 @@
         </is>
       </c>
       <c r="M124" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N124" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="125">
@@ -6802,7 +7924,7 @@
         <v>84000</v>
       </c>
       <c r="I125" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J125" t="n">
         <v>18500</v>
@@ -6816,7 +7938,16 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N125" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O125" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P125" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="126">
@@ -6853,7 +7984,7 @@
         <v>21000</v>
       </c>
       <c r="I126" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J126" t="n">
         <v>18500</v>
@@ -6867,7 +7998,16 @@
         </is>
       </c>
       <c r="M126" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N126" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O126" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P126" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="127">
@@ -6920,6 +8060,15 @@
       <c r="M127" t="n">
         <v>2500</v>
       </c>
+      <c r="N127" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6955,7 +8104,7 @@
         <v>42000</v>
       </c>
       <c r="I128" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J128" t="n">
         <v>18500</v>
@@ -6969,7 +8118,16 @@
         </is>
       </c>
       <c r="M128" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N128" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O128" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P128" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="129">
@@ -7006,7 +8164,7 @@
         <v>63000</v>
       </c>
       <c r="I129" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J129" t="n">
         <v>18500</v>
@@ -7020,7 +8178,16 @@
         </is>
       </c>
       <c r="M129" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N129" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O129" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P129" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="130">
@@ -7057,7 +8224,7 @@
         <v>63000</v>
       </c>
       <c r="I130" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J130" t="n">
         <v>18500</v>
@@ -7071,7 +8238,16 @@
         </is>
       </c>
       <c r="M130" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N130" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O130" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P130" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="131">
@@ -7124,6 +8300,15 @@
       <c r="M131" t="n">
         <v>65500</v>
       </c>
+      <c r="N131" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O131" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7159,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>225000</v>
+        <v>240300</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -7173,7 +8358,16 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>185000</v>
+        <v>200300</v>
+      </c>
+      <c r="N132" t="n">
+        <v>240300</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>200300</v>
       </c>
     </row>
     <row r="133">
@@ -7210,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -7224,7 +8418,16 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>90000</v>
+        <v>96120</v>
+      </c>
+      <c r="N133" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>96120</v>
       </c>
     </row>
     <row r="134">
@@ -7261,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -7275,7 +8478,16 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N134" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="135">
@@ -7312,7 +8524,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -7326,7 +8538,16 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N135" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="136">
@@ -7363,7 +8584,7 @@
         <v>21000</v>
       </c>
       <c r="I136" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J136" t="n">
         <v>18500</v>
@@ -7377,7 +8598,16 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N136" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O136" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P136" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="137">
@@ -7414,7 +8644,7 @@
         <v>21000</v>
       </c>
       <c r="I137" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J137" t="n">
         <v>18500</v>
@@ -7428,7 +8658,16 @@
         </is>
       </c>
       <c r="M137" t="n">
-        <v>142500</v>
+        <v>154740</v>
+      </c>
+      <c r="N137" t="n">
+        <v>213240</v>
+      </c>
+      <c r="O137" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P137" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="138">
@@ -7465,7 +8704,7 @@
         <v>21000</v>
       </c>
       <c r="I138" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J138" t="n">
         <v>18500</v>
@@ -7479,7 +8718,16 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N138" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O138" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P138" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="139">
@@ -7516,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -7530,7 +8778,16 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N139" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="140">
@@ -7567,7 +8824,7 @@
         <v>84000</v>
       </c>
       <c r="I140" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J140" t="n">
         <v>18500</v>
@@ -7581,7 +8838,16 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N140" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O140" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P140" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="141">
@@ -7634,6 +8900,15 @@
       <c r="M141" t="n">
         <v>44500</v>
       </c>
+      <c r="N141" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O141" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7669,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -7683,7 +8958,16 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N142" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="143">
@@ -7720,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -7734,7 +9018,16 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N143" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="144">
@@ -7787,6 +9080,15 @@
       <c r="M144" t="n">
         <v>86500</v>
       </c>
+      <c r="N144" t="n">
+        <v>105000</v>
+      </c>
+      <c r="O144" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7822,7 +9124,7 @@
         <v>21000</v>
       </c>
       <c r="I145" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J145" t="n">
         <v>18500</v>
@@ -7836,7 +9138,16 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N145" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O145" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P145" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="146">
@@ -7873,7 +9184,7 @@
         <v>21000</v>
       </c>
       <c r="I146" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J146" t="n">
         <v>18500</v>
@@ -7887,7 +9198,16 @@
         </is>
       </c>
       <c r="M146" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N146" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O146" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P146" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="147">
@@ -7924,7 +9244,7 @@
         <v>63000</v>
       </c>
       <c r="I147" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J147" t="n">
         <v>18500</v>
@@ -7938,7 +9258,16 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>94500</v>
+        <v>100620</v>
+      </c>
+      <c r="N147" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O147" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P147" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="148">
@@ -7975,7 +9304,7 @@
         <v>21000</v>
       </c>
       <c r="I148" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J148" t="n">
         <v>18500</v>
@@ -7989,7 +9318,16 @@
         </is>
       </c>
       <c r="M148" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N148" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O148" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P148" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="149">
@@ -8026,7 +9364,7 @@
         <v>21000</v>
       </c>
       <c r="I149" t="n">
-        <v>135000</v>
+        <v>192240</v>
       </c>
       <c r="J149" t="n">
         <v>18500</v>
@@ -8040,7 +9378,16 @@
         </is>
       </c>
       <c r="M149" t="n">
-        <v>97500</v>
+        <v>154740</v>
+      </c>
+      <c r="N149" t="n">
+        <v>213240</v>
+      </c>
+      <c r="O149" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P149" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="150">
@@ -8077,7 +9424,7 @@
         <v>21000</v>
       </c>
       <c r="I150" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J150" t="n">
         <v>18500</v>
@@ -8091,7 +9438,16 @@
         </is>
       </c>
       <c r="M150" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N150" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O150" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P150" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="151">
@@ -8128,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -8142,7 +9498,16 @@
         </is>
       </c>
       <c r="M151" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N151" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="152">
@@ -8179,7 +9544,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -8193,7 +9558,16 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N152" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="153">
@@ -8230,7 +9604,7 @@
         <v>21000</v>
       </c>
       <c r="I153" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J153" t="n">
         <v>18500</v>
@@ -8244,7 +9618,16 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N153" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O153" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P153" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="154">
@@ -8281,7 +9664,7 @@
         <v>63000</v>
       </c>
       <c r="I154" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J154" t="n">
         <v>18500</v>
@@ -8295,7 +9678,16 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>184500</v>
+        <v>196740</v>
+      </c>
+      <c r="N154" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O154" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P154" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="155">
@@ -8348,6 +9740,15 @@
       <c r="M155" t="n">
         <v>44500</v>
       </c>
+      <c r="N155" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O155" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8383,7 +9784,7 @@
         <v>63000</v>
       </c>
       <c r="I156" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J156" t="n">
         <v>18500</v>
@@ -8397,7 +9798,16 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N156" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O156" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P156" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="157">
@@ -8434,7 +9844,7 @@
         <v>21000</v>
       </c>
       <c r="I157" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J157" t="n">
         <v>18500</v>
@@ -8448,7 +9858,16 @@
         </is>
       </c>
       <c r="M157" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N157" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O157" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P157" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="158">
@@ -8485,7 +9904,7 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -8499,7 +9918,16 @@
         </is>
       </c>
       <c r="M158" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N158" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="159">
@@ -8536,7 +9964,7 @@
         <v>21000</v>
       </c>
       <c r="I159" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J159" t="n">
         <v>18500</v>
@@ -8550,7 +9978,16 @@
         </is>
       </c>
       <c r="M159" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N159" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P159" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="160">
@@ -8587,7 +10024,7 @@
         <v>63000</v>
       </c>
       <c r="I160" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J160" t="n">
         <v>18500</v>
@@ -8601,7 +10038,16 @@
         </is>
       </c>
       <c r="M160" t="n">
-        <v>184500</v>
+        <v>196740</v>
+      </c>
+      <c r="N160" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O160" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P160" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="161">
@@ -8638,7 +10084,7 @@
         <v>42000</v>
       </c>
       <c r="I161" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J161" t="n">
         <v>18500</v>
@@ -8652,7 +10098,16 @@
         </is>
       </c>
       <c r="M161" t="n">
-        <v>73500</v>
+        <v>79620</v>
+      </c>
+      <c r="N161" t="n">
+        <v>138120</v>
+      </c>
+      <c r="O161" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P161" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="162">
@@ -8689,7 +10144,7 @@
         <v>21000</v>
       </c>
       <c r="I162" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -8701,6 +10156,13 @@
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O162" t="n">
+        <v>21000</v>
+      </c>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8752,6 +10214,15 @@
       <c r="M163" t="n">
         <v>23500</v>
       </c>
+      <c r="N163" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O163" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8787,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -8801,7 +10272,16 @@
         </is>
       </c>
       <c r="M164" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N164" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="165">
@@ -8838,7 +10318,7 @@
         <v>63000</v>
       </c>
       <c r="I165" t="n">
-        <v>135000</v>
+        <v>96120</v>
       </c>
       <c r="J165" t="n">
         <v>18500</v>
@@ -8852,7 +10332,16 @@
         </is>
       </c>
       <c r="M165" t="n">
-        <v>139500</v>
+        <v>100620</v>
+      </c>
+      <c r="N165" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O165" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P165" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="166">
@@ -8889,7 +10378,7 @@
         <v>84000</v>
       </c>
       <c r="I166" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J166" t="n">
         <v>18500</v>
@@ -8903,7 +10392,16 @@
         </is>
       </c>
       <c r="M166" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N166" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O166" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P166" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="167">
@@ -8940,7 +10438,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J167" t="n">
         <v>18500</v>
@@ -8954,7 +10452,16 @@
         </is>
       </c>
       <c r="M167" t="n">
-        <v>-13500</v>
+        <v>-10440</v>
+      </c>
+      <c r="N167" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O167" t="n">
+        <v>-18500</v>
+      </c>
+      <c r="P167" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="168">
@@ -8991,7 +10498,7 @@
         <v>21000</v>
       </c>
       <c r="I168" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J168" t="n">
         <v>18500</v>
@@ -9005,7 +10512,16 @@
         </is>
       </c>
       <c r="M168" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N168" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O168" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P168" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="169">
@@ -9042,7 +10558,7 @@
         <v>84000</v>
       </c>
       <c r="I169" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J169" t="n">
         <v>18500</v>
@@ -9056,7 +10572,16 @@
         </is>
       </c>
       <c r="M169" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N169" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O169" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P169" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="170">
@@ -9109,6 +10634,15 @@
       <c r="M170" t="n">
         <v>44500</v>
       </c>
+      <c r="N170" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O170" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9144,7 +10678,7 @@
         <v>63000</v>
       </c>
       <c r="I171" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J171" t="n">
         <v>18500</v>
@@ -9158,7 +10692,16 @@
         </is>
       </c>
       <c r="M171" t="n">
-        <v>94500</v>
+        <v>100620</v>
+      </c>
+      <c r="N171" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O171" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P171" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="172">
@@ -9195,7 +10738,7 @@
         <v>21000</v>
       </c>
       <c r="I172" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -9209,7 +10752,16 @@
         </is>
       </c>
       <c r="M172" t="n">
-        <v>71000</v>
+        <v>77120</v>
+      </c>
+      <c r="N172" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O172" t="n">
+        <v>21000</v>
+      </c>
+      <c r="P172" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="173">
@@ -9246,7 +10798,7 @@
         <v>21000</v>
       </c>
       <c r="I173" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J173" t="n">
         <v>18500</v>
@@ -9260,7 +10812,16 @@
         </is>
       </c>
       <c r="M173" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N173" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O173" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P173" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="174">
@@ -9297,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -9311,7 +10872,16 @@
         </is>
       </c>
       <c r="M174" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N174" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="175">
@@ -9348,7 +10918,7 @@
         <v>168000</v>
       </c>
       <c r="I175" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J175" t="n">
         <v>18500</v>
@@ -9362,7 +10932,16 @@
         </is>
       </c>
       <c r="M175" t="n">
-        <v>289500</v>
+        <v>301740</v>
+      </c>
+      <c r="N175" t="n">
+        <v>360240</v>
+      </c>
+      <c r="O175" t="n">
+        <v>149500</v>
+      </c>
+      <c r="P175" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="176">
@@ -9399,7 +10978,7 @@
         <v>63000</v>
       </c>
       <c r="I176" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J176" t="n">
         <v>18500</v>
@@ -9413,7 +10992,16 @@
         </is>
       </c>
       <c r="M176" t="n">
-        <v>94500</v>
+        <v>100620</v>
+      </c>
+      <c r="N176" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O176" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P176" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="177">
@@ -9450,7 +11038,7 @@
         <v>21000</v>
       </c>
       <c r="I177" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J177" t="n">
         <v>18500</v>
@@ -9464,7 +11052,16 @@
         </is>
       </c>
       <c r="M177" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N177" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O177" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P177" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="178">
@@ -9501,7 +11098,7 @@
         <v>42000</v>
       </c>
       <c r="I178" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J178" t="n">
         <v>18500</v>
@@ -9515,7 +11112,16 @@
         </is>
       </c>
       <c r="M178" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N178" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O178" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P178" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="179">
@@ -9552,7 +11158,7 @@
         <v>21000</v>
       </c>
       <c r="I179" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J179" t="n">
         <v>18500</v>
@@ -9566,7 +11172,16 @@
         </is>
       </c>
       <c r="M179" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N179" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O179" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P179" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="180">
@@ -9603,7 +11218,7 @@
         <v>63000</v>
       </c>
       <c r="I180" t="n">
-        <v>135000</v>
+        <v>96120</v>
       </c>
       <c r="J180" t="n">
         <v>18500</v>
@@ -9617,7 +11232,16 @@
         </is>
       </c>
       <c r="M180" t="n">
-        <v>139500</v>
+        <v>100620</v>
+      </c>
+      <c r="N180" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O180" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P180" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="181">
@@ -9654,7 +11278,7 @@
         <v>84000</v>
       </c>
       <c r="I181" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J181" t="n">
         <v>18500</v>
@@ -9668,7 +11292,16 @@
         </is>
       </c>
       <c r="M181" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N181" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O181" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P181" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="182">
@@ -9705,7 +11338,7 @@
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -9719,7 +11352,16 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N182" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="183">
@@ -9772,6 +11414,15 @@
       <c r="M183" t="n">
         <v>23500</v>
       </c>
+      <c r="N183" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O183" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9807,7 +11458,7 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>225000</v>
+        <v>240300</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -9821,7 +11472,16 @@
         </is>
       </c>
       <c r="M184" t="n">
-        <v>185000</v>
+        <v>200300</v>
+      </c>
+      <c r="N184" t="n">
+        <v>240300</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>200300</v>
       </c>
     </row>
     <row r="185">
@@ -9858,7 +11518,7 @@
         <v>84000</v>
       </c>
       <c r="I185" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J185" t="n">
         <v>18500</v>
@@ -9872,7 +11532,16 @@
         </is>
       </c>
       <c r="M185" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N185" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O185" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P185" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="186">
@@ -9925,6 +11594,15 @@
       <c r="M186" t="n">
         <v>23500</v>
       </c>
+      <c r="N186" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O186" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9960,7 +11638,7 @@
         <v>21000</v>
       </c>
       <c r="I187" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -9974,7 +11652,16 @@
         </is>
       </c>
       <c r="M187" t="n">
-        <v>71000</v>
+        <v>77120</v>
+      </c>
+      <c r="N187" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O187" t="n">
+        <v>21000</v>
+      </c>
+      <c r="P187" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="188">
@@ -10027,6 +11714,15 @@
       <c r="M188" t="n">
         <v>23500</v>
       </c>
+      <c r="N188" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O188" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -10062,7 +11758,7 @@
         <v>63000</v>
       </c>
       <c r="I189" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J189" t="n">
         <v>18500</v>
@@ -10076,7 +11772,16 @@
         </is>
       </c>
       <c r="M189" t="n">
-        <v>184500</v>
+        <v>196740</v>
+      </c>
+      <c r="N189" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O189" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P189" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="190">
@@ -10110,7 +11815,7 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>168000</v>
+        <v>336000</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -10127,7 +11832,16 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>149500</v>
+        <v>317500</v>
+      </c>
+      <c r="N190" t="n">
+        <v>336000</v>
+      </c>
+      <c r="O190" t="n">
+        <v>317500</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -10180,6 +11894,15 @@
       <c r="M191" t="n">
         <v>23500</v>
       </c>
+      <c r="N191" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O191" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -10215,7 +11938,7 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="n">
@@ -10227,6 +11950,13 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
+      <c r="N192" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="n">
+        <v>56120</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -10262,7 +11992,7 @@
         <v>42000</v>
       </c>
       <c r="I193" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J193" t="n">
         <v>18500</v>
@@ -10276,7 +12006,16 @@
         </is>
       </c>
       <c r="M193" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N193" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O193" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P193" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="194">
@@ -10313,7 +12052,7 @@
         <v>21000</v>
       </c>
       <c r="I194" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J194" t="n">
         <v>18500</v>
@@ -10327,7 +12066,16 @@
         </is>
       </c>
       <c r="M194" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N194" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O194" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P194" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="195">
@@ -10364,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -10378,7 +12126,16 @@
         </is>
       </c>
       <c r="M195" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N195" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="196">
@@ -10415,7 +12172,7 @@
         <v>105000</v>
       </c>
       <c r="I196" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J196" t="n">
         <v>18500</v>
@@ -10429,7 +12186,16 @@
         </is>
       </c>
       <c r="M196" t="n">
-        <v>229380</v>
+        <v>238740</v>
+      </c>
+      <c r="N196" t="n">
+        <v>297240</v>
+      </c>
+      <c r="O196" t="n">
+        <v>86500</v>
+      </c>
+      <c r="P196" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="197">
@@ -10466,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -10480,7 +12246,16 @@
         </is>
       </c>
       <c r="M197" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N197" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="198">
@@ -10517,7 +12292,7 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -10531,7 +12306,16 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N198" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="199">
@@ -10568,7 +12352,7 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>225000</v>
+        <v>240300</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -10582,7 +12366,16 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>185000</v>
+        <v>200300</v>
+      </c>
+      <c r="N199" t="n">
+        <v>240300</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>200300</v>
       </c>
     </row>
     <row r="200">
@@ -10619,7 +12412,7 @@
         <v>42000</v>
       </c>
       <c r="I200" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J200" t="n">
         <v>18500</v>
@@ -10633,7 +12426,16 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>28500</v>
+        <v>31560</v>
+      </c>
+      <c r="N200" t="n">
+        <v>90060</v>
+      </c>
+      <c r="O200" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P200" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="201">
@@ -10686,6 +12488,15 @@
       <c r="M201" t="n">
         <v>44500</v>
       </c>
+      <c r="N201" t="n">
+        <v>63000</v>
+      </c>
+      <c r="O201" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10721,7 +12532,7 @@
         <v>21000</v>
       </c>
       <c r="I202" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J202" t="n">
         <v>18500</v>
@@ -10735,7 +12546,16 @@
         </is>
       </c>
       <c r="M202" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N202" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O202" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P202" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="203">
@@ -10772,7 +12592,7 @@
         <v>21000</v>
       </c>
       <c r="I203" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J203" t="n">
         <v>18500</v>
@@ -10786,7 +12606,16 @@
         </is>
       </c>
       <c r="M203" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N203" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O203" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P203" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="204">
@@ -10823,7 +12652,7 @@
         <v>21000</v>
       </c>
       <c r="I204" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J204" t="n">
         <v>18500</v>
@@ -10837,7 +12666,16 @@
         </is>
       </c>
       <c r="M204" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N204" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O204" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P204" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="205">
@@ -10874,7 +12712,7 @@
         <v>84000</v>
       </c>
       <c r="I205" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J205" t="n">
         <v>18500</v>
@@ -10888,7 +12726,16 @@
         </is>
       </c>
       <c r="M205" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N205" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O205" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P205" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="206">
@@ -10941,6 +12788,15 @@
       <c r="M206" t="n">
         <v>23500</v>
       </c>
+      <c r="N206" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O206" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10976,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -10990,7 +12846,16 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N207" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="208">
@@ -11043,6 +12908,15 @@
       <c r="M208" t="n">
         <v>23500</v>
       </c>
+      <c r="N208" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O208" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11078,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -11092,7 +12966,16 @@
         </is>
       </c>
       <c r="M209" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N209" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="210">
@@ -11145,6 +13028,15 @@
       <c r="M210" t="n">
         <v>65500</v>
       </c>
+      <c r="N210" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O210" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -11180,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -11194,7 +13086,16 @@
         </is>
       </c>
       <c r="M211" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N211" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="212">
@@ -11231,7 +13132,7 @@
         <v>21000</v>
       </c>
       <c r="I212" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J212" t="n">
         <v>18500</v>
@@ -11245,7 +13146,16 @@
         </is>
       </c>
       <c r="M212" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N212" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O212" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P212" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="213">
@@ -11282,7 +13192,7 @@
         <v>21000</v>
       </c>
       <c r="I213" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J213" t="n">
         <v>18500</v>
@@ -11296,7 +13206,16 @@
         </is>
       </c>
       <c r="M213" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N213" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O213" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P213" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="214">
@@ -11333,7 +13252,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -11347,7 +13266,16 @@
         </is>
       </c>
       <c r="M214" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N214" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="215">
@@ -11400,6 +13328,15 @@
       <c r="M215" t="n">
         <v>65500</v>
       </c>
+      <c r="N215" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O215" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11435,7 +13372,7 @@
         <v>63000</v>
       </c>
       <c r="I216" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J216" t="n">
         <v>18500</v>
@@ -11449,7 +13386,16 @@
         </is>
       </c>
       <c r="M216" t="n">
-        <v>94500</v>
+        <v>100620</v>
+      </c>
+      <c r="N216" t="n">
+        <v>159120</v>
+      </c>
+      <c r="O216" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P216" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="217">
@@ -11486,7 +13432,7 @@
         <v>21000</v>
       </c>
       <c r="I217" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J217" t="n">
         <v>18500</v>
@@ -11500,7 +13446,16 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N217" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O217" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P217" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="218">
@@ -11537,7 +13492,7 @@
         <v>21000</v>
       </c>
       <c r="I218" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J218" t="n">
         <v>18500</v>
@@ -11551,7 +13506,16 @@
         </is>
       </c>
       <c r="M218" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N218" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O218" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P218" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="219">
@@ -11588,7 +13552,7 @@
         <v>63000</v>
       </c>
       <c r="I219" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J219" t="n">
         <v>18500</v>
@@ -11602,7 +13566,16 @@
         </is>
       </c>
       <c r="M219" t="n">
-        <v>184500</v>
+        <v>196740</v>
+      </c>
+      <c r="N219" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O219" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P219" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="220">
@@ -11636,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>168000</v>
+        <v>336000</v>
       </c>
       <c r="I220" t="n">
         <v>0</v>
@@ -11653,7 +13626,16 @@
         </is>
       </c>
       <c r="M220" t="n">
-        <v>149500</v>
+        <v>317500</v>
+      </c>
+      <c r="N220" t="n">
+        <v>336000</v>
+      </c>
+      <c r="O220" t="n">
+        <v>317500</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -11690,7 +13672,7 @@
         <v>21000</v>
       </c>
       <c r="I221" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J221" t="n">
         <v>18500</v>
@@ -11704,7 +13686,16 @@
         </is>
       </c>
       <c r="M221" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N221" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O221" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P221" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="222">
@@ -11741,7 +13732,7 @@
         <v>21000</v>
       </c>
       <c r="I222" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J222" t="n">
         <v>18500</v>
@@ -11755,7 +13746,16 @@
         </is>
       </c>
       <c r="M222" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N222" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O222" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P222" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="223">
@@ -11792,7 +13792,7 @@
         <v>21000</v>
       </c>
       <c r="I223" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J223" t="n">
         <v>18500</v>
@@ -11806,7 +13806,16 @@
         </is>
       </c>
       <c r="M223" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N223" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O223" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P223" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="224">
@@ -11843,7 +13852,7 @@
         <v>21000</v>
       </c>
       <c r="I224" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J224" t="n">
         <v>18500</v>
@@ -11857,7 +13866,16 @@
         </is>
       </c>
       <c r="M224" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N224" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O224" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P224" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="225">
@@ -11894,7 +13912,7 @@
         <v>84000</v>
       </c>
       <c r="I225" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J225" t="n">
         <v>18500</v>
@@ -11908,7 +13926,16 @@
         </is>
       </c>
       <c r="M225" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N225" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O225" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P225" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="226">
@@ -11945,7 +13972,7 @@
         <v>63000</v>
       </c>
       <c r="I226" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J226" t="n">
         <v>18500</v>
@@ -11959,7 +13986,16 @@
         </is>
       </c>
       <c r="M226" t="n">
-        <v>187380</v>
+        <v>196740</v>
+      </c>
+      <c r="N226" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O226" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P226" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="227">
@@ -11996,7 +14032,7 @@
         <v>21000</v>
       </c>
       <c r="I227" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J227" t="n">
         <v>18500</v>
@@ -12010,7 +14046,16 @@
         </is>
       </c>
       <c r="M227" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N227" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O227" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P227" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="228">
@@ -12063,6 +14108,15 @@
       <c r="M228" t="n">
         <v>23500</v>
       </c>
+      <c r="N228" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O228" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -12098,7 +14152,7 @@
         <v>84000</v>
       </c>
       <c r="I229" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J229" t="n">
         <v>18500</v>
@@ -12112,7 +14166,16 @@
         </is>
       </c>
       <c r="M229" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N229" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O229" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P229" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="230">
@@ -12149,7 +14212,7 @@
         <v>21000</v>
       </c>
       <c r="I230" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J230" t="n">
         <v>18500</v>
@@ -12163,7 +14226,16 @@
         </is>
       </c>
       <c r="M230" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N230" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O230" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P230" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="231">
@@ -12200,7 +14272,7 @@
         <v>63000</v>
       </c>
       <c r="I231" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J231" t="n">
         <v>18500</v>
@@ -12214,7 +14286,16 @@
         </is>
       </c>
       <c r="M231" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N231" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O231" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P231" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="232">
@@ -12251,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -12265,7 +14346,16 @@
         </is>
       </c>
       <c r="M232" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N232" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="233">
@@ -12302,7 +14392,7 @@
         <v>21000</v>
       </c>
       <c r="I233" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J233" t="n">
         <v>18500</v>
@@ -12316,7 +14406,16 @@
         </is>
       </c>
       <c r="M233" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N233" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O233" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P233" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="234">
@@ -12353,7 +14452,7 @@
         <v>21000</v>
       </c>
       <c r="I234" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J234" t="n">
         <v>18500</v>
@@ -12367,7 +14466,16 @@
         </is>
       </c>
       <c r="M234" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N234" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O234" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P234" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="235">
@@ -12404,7 +14512,7 @@
         <v>84000</v>
       </c>
       <c r="I235" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J235" t="n">
         <v>18500</v>
@@ -12418,7 +14526,16 @@
         </is>
       </c>
       <c r="M235" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N235" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O235" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P235" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="236">
@@ -12455,7 +14572,7 @@
         <v>21000</v>
       </c>
       <c r="I236" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J236" t="n">
         <v>18500</v>
@@ -12469,7 +14586,16 @@
         </is>
       </c>
       <c r="M236" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N236" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O236" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P236" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="237">
@@ -12522,6 +14648,15 @@
       <c r="M237" t="n">
         <v>2500</v>
       </c>
+      <c r="N237" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O237" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -12557,7 +14692,7 @@
         <v>21000</v>
       </c>
       <c r="I238" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J238" t="n">
         <v>18500</v>
@@ -12571,7 +14706,16 @@
         </is>
       </c>
       <c r="M238" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N238" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O238" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P238" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="239">
@@ -12608,7 +14752,7 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -12622,7 +14766,16 @@
         </is>
       </c>
       <c r="M239" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N239" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="240">
@@ -12675,6 +14828,15 @@
       <c r="M240" t="n">
         <v>65500</v>
       </c>
+      <c r="N240" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O240" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -12710,7 +14872,7 @@
         <v>84000</v>
       </c>
       <c r="I241" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J241" t="n">
         <v>18500</v>
@@ -12724,7 +14886,16 @@
         </is>
       </c>
       <c r="M241" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N241" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O241" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P241" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="242">
@@ -12761,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -12775,7 +14946,16 @@
         </is>
       </c>
       <c r="M242" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N242" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="243">
@@ -12812,7 +14992,7 @@
         <v>21000</v>
       </c>
       <c r="I243" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J243" t="n">
         <v>18500</v>
@@ -12826,7 +15006,16 @@
         </is>
       </c>
       <c r="M243" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N243" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O243" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P243" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="244">
@@ -12863,7 +15052,7 @@
         <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>225000</v>
+        <v>240300</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -12877,7 +15066,16 @@
         </is>
       </c>
       <c r="M244" t="n">
-        <v>185000</v>
+        <v>200300</v>
+      </c>
+      <c r="N244" t="n">
+        <v>240300</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>200300</v>
       </c>
     </row>
     <row r="245">
@@ -12930,6 +15128,15 @@
       <c r="M245" t="n">
         <v>65500</v>
       </c>
+      <c r="N245" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O245" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -12965,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -12979,7 +15186,16 @@
         </is>
       </c>
       <c r="M246" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N246" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="247">
@@ -13032,6 +15248,15 @@
       <c r="M247" t="n">
         <v>2500</v>
       </c>
+      <c r="N247" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O247" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -13067,7 +15292,7 @@
         <v>21000</v>
       </c>
       <c r="I248" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J248" t="n">
         <v>18500</v>
@@ -13081,7 +15306,16 @@
         </is>
       </c>
       <c r="M248" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N248" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O248" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P248" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="249">
@@ -13118,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -13132,7 +15366,16 @@
         </is>
       </c>
       <c r="M249" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N249" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="250">
@@ -13169,7 +15412,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -13183,7 +15426,16 @@
         </is>
       </c>
       <c r="M250" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N250" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="251">
@@ -13220,7 +15472,7 @@
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -13234,7 +15486,16 @@
         </is>
       </c>
       <c r="M251" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N251" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="252">
@@ -13271,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -13285,7 +15546,16 @@
         </is>
       </c>
       <c r="M252" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N252" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="253">
@@ -13322,7 +15592,7 @@
         <v>21000</v>
       </c>
       <c r="I253" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J253" t="n">
         <v>18500</v>
@@ -13336,7 +15606,16 @@
         </is>
       </c>
       <c r="M253" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N253" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O253" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P253" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="254">
@@ -13373,7 +15652,7 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -13387,7 +15666,16 @@
         </is>
       </c>
       <c r="M254" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N254" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="255">
@@ -13440,6 +15728,15 @@
       <c r="M255" t="n">
         <v>65500</v>
       </c>
+      <c r="N255" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O255" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -13475,7 +15772,7 @@
         <v>63000</v>
       </c>
       <c r="I256" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J256" t="n">
         <v>18500</v>
@@ -13489,7 +15786,16 @@
         </is>
       </c>
       <c r="M256" t="n">
-        <v>139500</v>
+        <v>148680</v>
+      </c>
+      <c r="N256" t="n">
+        <v>207180</v>
+      </c>
+      <c r="O256" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P256" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="257">
@@ -13526,7 +15832,7 @@
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -13540,7 +15846,16 @@
         </is>
       </c>
       <c r="M257" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N257" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="258">
@@ -13577,7 +15892,7 @@
         <v>21000</v>
       </c>
       <c r="I258" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J258" t="n">
         <v>18500</v>
@@ -13591,7 +15906,16 @@
         </is>
       </c>
       <c r="M258" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N258" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O258" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P258" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="259">
@@ -13628,7 +15952,7 @@
         <v>84000</v>
       </c>
       <c r="I259" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J259" t="n">
         <v>18500</v>
@@ -13642,7 +15966,16 @@
         </is>
       </c>
       <c r="M259" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N259" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O259" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P259" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="260">
@@ -13679,7 +16012,7 @@
         <v>84000</v>
       </c>
       <c r="I260" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J260" t="n">
         <v>18500</v>
@@ -13693,7 +16026,16 @@
         </is>
       </c>
       <c r="M260" t="n">
-        <v>245500</v>
+        <v>257740</v>
+      </c>
+      <c r="N260" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O260" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P260" t="n">
+        <v>192240</v>
       </c>
     </row>
     <row r="261">
@@ -13730,7 +16072,7 @@
         <v>42000</v>
       </c>
       <c r="I261" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J261" t="n">
         <v>18500</v>
@@ -13744,7 +16086,16 @@
         </is>
       </c>
       <c r="M261" t="n">
-        <v>73500</v>
+        <v>79620</v>
+      </c>
+      <c r="N261" t="n">
+        <v>138120</v>
+      </c>
+      <c r="O261" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P261" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="262">
@@ -13781,7 +16132,7 @@
         <v>21000</v>
       </c>
       <c r="I262" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J262" t="n">
         <v>18500</v>
@@ -13795,7 +16146,16 @@
         </is>
       </c>
       <c r="M262" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N262" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O262" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P262" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="263">
@@ -13832,7 +16192,7 @@
         <v>21000</v>
       </c>
       <c r="I263" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J263" t="n">
         <v>18500</v>
@@ -13846,7 +16206,16 @@
         </is>
       </c>
       <c r="M263" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N263" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O263" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P263" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="264">
@@ -13883,7 +16252,7 @@
         <v>63000</v>
       </c>
       <c r="I264" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J264" t="n">
         <v>18500</v>
@@ -13897,7 +16266,16 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>184500</v>
+        <v>196740</v>
+      </c>
+      <c r="N264" t="n">
+        <v>255240</v>
+      </c>
+      <c r="O264" t="n">
+        <v>44500</v>
+      </c>
+      <c r="P264" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="265">
@@ -13950,6 +16328,15 @@
       <c r="M265" t="n">
         <v>65500</v>
       </c>
+      <c r="N265" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O265" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -14001,6 +16388,15 @@
       <c r="M266" t="n">
         <v>23500</v>
       </c>
+      <c r="N266" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O266" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -14036,7 +16432,7 @@
         <v>21000</v>
       </c>
       <c r="I267" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J267" t="n">
         <v>18500</v>
@@ -14050,7 +16446,16 @@
         </is>
       </c>
       <c r="M267" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N267" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O267" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P267" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="268">
@@ -14087,7 +16492,7 @@
         <v>21000</v>
       </c>
       <c r="I268" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J268" t="n">
         <v>18500</v>
@@ -14101,7 +16506,16 @@
         </is>
       </c>
       <c r="M268" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N268" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O268" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P268" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="269">
@@ -14138,7 +16552,7 @@
         <v>21000</v>
       </c>
       <c r="I269" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J269" t="n">
         <v>18500</v>
@@ -14152,7 +16566,16 @@
         </is>
       </c>
       <c r="M269" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N269" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O269" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P269" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="270">
@@ -14205,6 +16628,15 @@
       <c r="M270" t="n">
         <v>65500</v>
       </c>
+      <c r="N270" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O270" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -14240,7 +16672,7 @@
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -14254,7 +16686,16 @@
         </is>
       </c>
       <c r="M271" t="n">
-        <v>142880</v>
+        <v>152240</v>
+      </c>
+      <c r="N271" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="272">
@@ -14291,7 +16732,7 @@
         <v>21000</v>
       </c>
       <c r="I272" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J272" t="n">
         <v>18500</v>
@@ -14305,7 +16746,16 @@
         </is>
       </c>
       <c r="M272" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N272" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O272" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P272" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="273">
@@ -14342,7 +16792,7 @@
         <v>21000</v>
       </c>
       <c r="I273" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J273" t="n">
         <v>18500</v>
@@ -14356,7 +16806,16 @@
         </is>
       </c>
       <c r="M273" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N273" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O273" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P273" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="274">
@@ -14393,7 +16852,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>225000</v>
+        <v>240300</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -14407,7 +16866,16 @@
         </is>
       </c>
       <c r="M274" t="n">
-        <v>185000</v>
+        <v>200300</v>
+      </c>
+      <c r="N274" t="n">
+        <v>240300</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>200300</v>
       </c>
     </row>
     <row r="275">
@@ -14444,7 +16912,7 @@
         <v>84000</v>
       </c>
       <c r="I275" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J275" t="n">
         <v>18500</v>
@@ -14458,7 +16926,16 @@
         </is>
       </c>
       <c r="M275" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N275" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O275" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P275" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="276">
@@ -14495,7 +16972,7 @@
         <v>42000</v>
       </c>
       <c r="I276" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J276" t="n">
         <v>18500</v>
@@ -14509,7 +16986,16 @@
         </is>
       </c>
       <c r="M276" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N276" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O276" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P276" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="277">
@@ -14562,6 +17048,15 @@
       <c r="M277" t="n">
         <v>2500</v>
       </c>
+      <c r="N277" t="n">
+        <v>21000</v>
+      </c>
+      <c r="O277" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -14597,7 +17092,7 @@
         <v>21000</v>
       </c>
       <c r="I278" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J278" t="n">
         <v>18500</v>
@@ -14611,7 +17106,16 @@
         </is>
       </c>
       <c r="M278" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N278" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O278" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P278" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="279">
@@ -14648,7 +17152,7 @@
         <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -14662,7 +17166,16 @@
         </is>
       </c>
       <c r="M279" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N279" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="280">
@@ -14699,7 +17212,7 @@
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -14713,7 +17226,16 @@
         </is>
       </c>
       <c r="M280" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N280" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="281">
@@ -14750,7 +17272,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -14764,7 +17286,16 @@
         </is>
       </c>
       <c r="M281" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N281" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="282">
@@ -14801,7 +17332,7 @@
         <v>21000</v>
       </c>
       <c r="I282" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J282" t="n">
         <v>18500</v>
@@ -14815,7 +17346,16 @@
         </is>
       </c>
       <c r="M282" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N282" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O282" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P282" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="283">
@@ -14868,6 +17408,15 @@
       <c r="M283" t="n">
         <v>23500</v>
       </c>
+      <c r="N283" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O283" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -14903,7 +17452,7 @@
         <v>0</v>
       </c>
       <c r="I284" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -14917,7 +17466,16 @@
         </is>
       </c>
       <c r="M284" t="n">
-        <v>95000</v>
+        <v>104180</v>
+      </c>
+      <c r="N284" t="n">
+        <v>144180</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="285">
@@ -14970,6 +17528,15 @@
       <c r="M285" t="n">
         <v>65500</v>
       </c>
+      <c r="N285" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O285" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -15005,7 +17572,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -15019,7 +17586,16 @@
         </is>
       </c>
       <c r="M286" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N286" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="287">
@@ -15056,7 +17632,7 @@
         <v>21000</v>
       </c>
       <c r="I287" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J287" t="n">
         <v>18500</v>
@@ -15070,7 +17646,16 @@
         </is>
       </c>
       <c r="M287" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N287" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O287" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P287" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="288">
@@ -15107,7 +17692,7 @@
         <v>21000</v>
       </c>
       <c r="I288" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J288" t="n">
         <v>18500</v>
@@ -15121,7 +17706,16 @@
         </is>
       </c>
       <c r="M288" t="n">
-        <v>52500</v>
+        <v>58620</v>
+      </c>
+      <c r="N288" t="n">
+        <v>117120</v>
+      </c>
+      <c r="O288" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P288" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="289">
@@ -15158,7 +17752,7 @@
         <v>84000</v>
       </c>
       <c r="I289" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J289" t="n">
         <v>18500</v>
@@ -15172,7 +17766,16 @@
         </is>
       </c>
       <c r="M289" t="n">
-        <v>205500</v>
+        <v>217740</v>
+      </c>
+      <c r="N289" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O289" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P289" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="290">
@@ -15225,6 +17828,15 @@
       <c r="M290" t="n">
         <v>65500</v>
       </c>
+      <c r="N290" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O290" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -15260,7 +17872,7 @@
         <v>42000</v>
       </c>
       <c r="I291" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J291" t="n">
         <v>18500</v>
@@ -15274,7 +17886,16 @@
         </is>
       </c>
       <c r="M291" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N291" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O291" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P291" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="292">
@@ -15311,7 +17932,7 @@
         <v>21000</v>
       </c>
       <c r="I292" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J292" t="n">
         <v>18500</v>
@@ -15325,7 +17946,16 @@
         </is>
       </c>
       <c r="M292" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N292" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O292" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P292" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="293">
@@ -15362,7 +17992,7 @@
         <v>21000</v>
       </c>
       <c r="I293" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J293" t="n">
         <v>18500</v>
@@ -15376,7 +18006,16 @@
         </is>
       </c>
       <c r="M293" t="n">
-        <v>7500</v>
+        <v>10560</v>
+      </c>
+      <c r="N293" t="n">
+        <v>69060</v>
+      </c>
+      <c r="O293" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P293" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="294">
@@ -15413,7 +18052,7 @@
         <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>180000</v>
+        <v>192240</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -15427,7 +18066,16 @@
         </is>
       </c>
       <c r="M294" t="n">
-        <v>140000</v>
+        <v>152240</v>
+      </c>
+      <c r="N294" t="n">
+        <v>192240</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="295">
@@ -15464,7 +18112,7 @@
         <v>84000</v>
       </c>
       <c r="I295" t="n">
-        <v>182880</v>
+        <v>192240</v>
       </c>
       <c r="J295" t="n">
         <v>18500</v>
@@ -15478,7 +18126,16 @@
         </is>
       </c>
       <c r="M295" t="n">
-        <v>208380</v>
+        <v>217740</v>
+      </c>
+      <c r="N295" t="n">
+        <v>276240</v>
+      </c>
+      <c r="O295" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P295" t="n">
+        <v>152240</v>
       </c>
     </row>
     <row r="296">
@@ -15515,7 +18172,7 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>45000</v>
+        <v>48060</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -15529,7 +18186,16 @@
         </is>
       </c>
       <c r="M296" t="n">
-        <v>5000</v>
+        <v>8060</v>
+      </c>
+      <c r="N296" t="n">
+        <v>48060</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>8060</v>
       </c>
     </row>
     <row r="297">
@@ -15566,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="I297" t="n">
-        <v>90000</v>
+        <v>96120</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -15580,7 +18246,16 @@
         </is>
       </c>
       <c r="M297" t="n">
-        <v>50000</v>
+        <v>56120</v>
+      </c>
+      <c r="N297" t="n">
+        <v>96120</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" t="n">
+        <v>56120</v>
       </c>
     </row>
     <row r="298">
@@ -15617,7 +18292,7 @@
         <v>42000</v>
       </c>
       <c r="I298" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J298" t="n">
         <v>18500</v>
@@ -15631,7 +18306,16 @@
         </is>
       </c>
       <c r="M298" t="n">
-        <v>118500</v>
+        <v>127680</v>
+      </c>
+      <c r="N298" t="n">
+        <v>186180</v>
+      </c>
+      <c r="O298" t="n">
+        <v>23500</v>
+      </c>
+      <c r="P298" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="299">
@@ -15668,7 +18352,7 @@
         <v>21000</v>
       </c>
       <c r="I299" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J299" t="n">
         <v>18500</v>
@@ -15682,7 +18366,16 @@
         </is>
       </c>
       <c r="M299" t="n">
-        <v>97500</v>
+        <v>106680</v>
+      </c>
+      <c r="N299" t="n">
+        <v>165180</v>
+      </c>
+      <c r="O299" t="n">
+        <v>2500</v>
+      </c>
+      <c r="P299" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="300">
@@ -15719,7 +18412,7 @@
         <v>84000</v>
       </c>
       <c r="I300" t="n">
-        <v>135000</v>
+        <v>144180</v>
       </c>
       <c r="J300" t="n">
         <v>18500</v>
@@ -15733,7 +18426,16 @@
         </is>
       </c>
       <c r="M300" t="n">
-        <v>160500</v>
+        <v>169680</v>
+      </c>
+      <c r="N300" t="n">
+        <v>228180</v>
+      </c>
+      <c r="O300" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P300" t="n">
+        <v>104180</v>
       </c>
     </row>
     <row r="301">
@@ -15785,6 +18487,15 @@
       </c>
       <c r="M301" t="n">
         <v>65500</v>
+      </c>
+      <c r="N301" t="n">
+        <v>84000</v>
+      </c>
+      <c r="O301" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P301" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
